--- a/Docs/PigHistoric.xlsx
+++ b/Docs/PigHistoric.xlsx
@@ -8,8 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="125725"/>
 </workbook>
@@ -785,7 +783,7 @@
         <v>26776.136617840002</v>
       </c>
       <c r="H17" s="4">
-        <f t="shared" ref="H16:H18" si="0">+F17-E17</f>
+        <f t="shared" ref="H17:H18" si="0">+F17-E17</f>
         <v>-4053.4801961599987</v>
       </c>
     </row>
@@ -896,22 +894,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>